--- a/artfynd/A 14020-2023 artfynd.xlsx
+++ b/artfynd/A 14020-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14020-2023 artfynd.xlsx
+++ b/artfynd/A 14020-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1895,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112093591</v>
+        <v>112093593</v>
       </c>
       <c r="B12" t="n">
-        <v>103790</v>
+        <v>103829</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1907,37 +1907,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>340</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -1949,10 +1940,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>653798</v>
+        <v>653786</v>
       </c>
       <c r="R12" t="n">
-        <v>6576988</v>
+        <v>6577035</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1985,11 +1976,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ganska små och taniga. Översiktlig räkning och troligen finns fler på de båda dellokalerna.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2021,10 +2007,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112093593</v>
+        <v>112116035</v>
       </c>
       <c r="B13" t="n">
-        <v>103829</v>
+        <v>90856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2033,43 +2019,45 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>6003297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spricktaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum glaucopus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svarvartorp ca 400 m SO om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>653786</v>
+        <v>653795</v>
       </c>
       <c r="R13" t="n">
-        <v>6577035</v>
+        <v>6577004</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2104,12 +2092,18 @@
           <t>2023-09-14</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Kött ganska sprött (ej korkartat), ljusbrunt.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2130,126 +2124,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>112116035</v>
-      </c>
-      <c r="B14" t="n">
-        <v>90856</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>6003297</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Spricktaggsvamp</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Hydnellum glaucopus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Svarvartorp ca 400 m SO om, Upl</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>653795</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6577004</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Ekerö</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Ekerö</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2023-09-14</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2023-09-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kött ganska sprött (ej korkartat), ljusbrunt.</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Gles barrskog på sand (både tall och gran)</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
